--- a/m1/docs/test-cases.xlsx
+++ b/m1/docs/test-cases.xlsx
@@ -19,7 +19,7 @@
     <t>Aisle PII API Automation — API Test Cases   (Aisle API → PII service → DB validation)</t>
   </si>
   <si>
-    <t>Last run: 2026-10-05 05:09 UTC  ·  environment staging  ·  projects=api  ·  took 323.4s</t>
+    <t>Last run: 2026-10-07 03:44 UTC  ·  environment staging  ·  projects=api  ·  took 328.8s</t>
   </si>
   <si>
     <t>Total test cases: 109</t>

--- a/m1/docs/test-cases.xlsx
+++ b/m1/docs/test-cases.xlsx
@@ -19,7 +19,7 @@
     <t>Aisle PII API Automation — API Test Cases   (Aisle API → PII service → DB validation)</t>
   </si>
   <si>
-    <t>Last run: 2026-10-19 06:20 UTC  ·  environment staging  ·  projects=api  ·  took 330.3s</t>
+    <t>Last run: 2026-10-22 08:46 UTC  ·  environment staging  ·  projects=api  ·  took 351.8s</t>
   </si>
   <si>
     <t>Total test cases: 109</t>

--- a/m1/docs/test-cases.xlsx
+++ b/m1/docs/test-cases.xlsx
@@ -19,7 +19,7 @@
     <t>Aisle PII API Automation — API Test Cases   (Aisle API → PII service → DB validation)</t>
   </si>
   <si>
-    <t>Last run: 2026-10-23 17:55 UTC  ·  environment staging  ·  projects=api  ·  took 360.5s</t>
+    <t>Last run: 2026-10-25 14:58 UTC  ·  environment staging  ·  projects=api  ·  took 356.6s</t>
   </si>
   <si>
     <t>Total test cases: 109</t>

--- a/m1/docs/test-cases.xlsx
+++ b/m1/docs/test-cases.xlsx
@@ -19,7 +19,7 @@
     <t>Aisle PII API Automation — API Test Cases   (Aisle API → PII service → DB validation)</t>
   </si>
   <si>
-    <t>Last run: 2026-10-26 05:00 UTC  ·  environment staging  ·  projects=api  ·  took 330.4s</t>
+    <t>Last run: 2026-10-28 04:24 UTC  ·  environment staging  ·  projects=api  ·  took 332.2s</t>
   </si>
   <si>
     <t>Total test cases: 109</t>

--- a/m1/docs/test-cases.xlsx
+++ b/m1/docs/test-cases.xlsx
@@ -19,7 +19,7 @@
     <t>Aisle PII API Automation — API Test Cases   (Aisle API → PII service → DB validation)</t>
   </si>
   <si>
-    <t>Last run: 2026-10-28 04:24 UTC  ·  environment staging  ·  projects=api  ·  took 332.2s</t>
+    <t>Last run: 2026-10-29 03:54 UTC  ·  environment staging  ·  projects=api  ·  took 382.4s</t>
   </si>
   <si>
     <t>Total test cases: 109</t>
